--- a/tests/mame/fixtures/KURO_test.xlsx
+++ b/tests/mame/fixtures/KURO_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd List" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="expected_mutations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fwd List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="expected_mutations" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -641,7 +641,6 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>V5F</t>
@@ -687,7 +686,6 @@
           <t>AAC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>K53N</t>
